--- a/implementation/policy-assist-urls/policy-assist-urls.xlsx
+++ b/implementation/policy-assist-urls/policy-assist-urls.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steven\GitHub-Repositories\Repositories\azure-policy-assistant-rag-solution-docs\implementation\policy-assist-urls\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2D528E-CC47-4DF9-8B01-FADB56242393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$2:$E$2</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -18,10 +28,548 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="117">
+  <si>
+    <t>https://github.com/Steven908263/azure-policy-assistant-react-chat-ui-dev</t>
+  </si>
+  <si>
+    <t>https://polite-ground-0d2a97a1e.6.azurestaticapps.net/</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Policy Assistant - React Client</t>
+  </si>
+  <si>
+    <t>Policy Assistant - React Client - GitHub Repository</t>
+  </si>
+  <si>
+    <t>https://polite-ground-0d2a97a1e.6.azurestaticapps.net</t>
+  </si>
+  <si>
+    <t>Row ID</t>
+  </si>
+  <si>
+    <t>39408db2c49a3db312ae631c4cd13ab3a2ee506d01aef597c81da346711b150306-886e53d0-12d3-4240-af62-8765903eb71b01e25060d2a97a1e</t>
+  </si>
+  <si>
+    <t>Policy Assistant - React Client -GitHub Repository - URL</t>
+  </si>
+  <si>
+    <t>Policy Assistant - React Client - Development - URL</t>
+  </si>
+  <si>
+    <t>Local laptop Policy Assistant React Client - URL</t>
+  </si>
+  <si>
+    <t>Policy Assistant - React Client - Azure Static Web Apps - Deployment Token</t>
+  </si>
+  <si>
+    <t>Function API</t>
+  </si>
+  <si>
+    <t>https://policy-assist-orchestration-func-app-dev-cxarefhbeef6e6d7.westus3-01.azurewebsites.net/api</t>
+  </si>
+  <si>
+    <t>Entra redirect</t>
+  </si>
+  <si>
+    <t>https://polite-ground-0d2a97a1e.6.azurestaticapps.net/redirect.html</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Azure</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Steven's Laptop</t>
+  </si>
+  <si>
+    <t>Azure Function Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Azure Static Web Apps</t>
+  </si>
+  <si>
+    <t>Configuration Item</t>
+  </si>
+  <si>
+    <t>Current Development Value</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>React API base URL</t>
+  </si>
+  <si>
+    <t>✅ Known</t>
+  </si>
+  <si>
+    <t>Policy Chat API URL</t>
+  </si>
+  <si>
+    <t>https://policy-assist-orchestration-func-app-dev-cxarefhbeef6e6d7.westus3-01.azurewebsites.net/api/policy-chat</t>
+  </si>
+  <si>
+    <t>Entra Tenant ID</t>
+  </si>
+  <si>
+    <t>619f6c56-0d58-43ac-b0f5-c3d155b63925</t>
+  </si>
+  <si>
+    <t>Entra Client ID</t>
+  </si>
+  <si>
+    <t>We have previously used an application/client ID in the project, but I want to verify which registration is currently wired into the deployed React client before locking this into I-20.</t>
+  </si>
+  <si>
+    <t>⚠️ Confirm</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/redirect.html</t>
+  </si>
+  <si>
+    <t>Redirect URI — Hosted Dev</t>
+  </si>
+  <si>
+    <r>
+      <t>${window.location.origin}/redirect.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, which resolves to the Development Static Web App's </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/redirect.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> URL</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ Implemented; exact hostname should be recorded</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A delegated Policy Assistant scope has been implemented. An earlier value was </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>api://cfc6f96e-9d3c-4b29-b09d-44bab3055d31/test_policy_assistant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; we should verify this is still the active Development scope.</t>
+    </r>
+  </si>
+  <si>
+    <t>Function App name</t>
+  </si>
+  <si>
+    <t>policy-assist-orchestration-func-app-dev</t>
+  </si>
+  <si>
+    <t>Function App URL</t>
+  </si>
+  <si>
+    <t>https://policy-assist-orchestration-func-app-dev-cxarefhbeef6e6d7.westus3-01.azurewebsites.net</t>
+  </si>
+  <si>
+    <t>Azure AI Search endpoint</t>
+  </si>
+  <si>
+    <t>https://as-corp-policy-ai-rag-search-svc-dev.search.windows.net</t>
+  </si>
+  <si>
+    <t>Azure AI Search index</t>
+  </si>
+  <si>
+    <t>index-policy-assist-ai-search-v2</t>
+  </si>
+  <si>
+    <t>Azure OpenAI / Foundry endpoint</t>
+  </si>
+  <si>
+    <t>https://rs-corp-policy-ai-rag-mf-dev.openai.azure.com</t>
+  </si>
+  <si>
+    <t>Model deployment name</t>
+  </si>
+  <si>
+    <t>gpt-5.4-mini</t>
+  </si>
+  <si>
+    <t>Cosmos endpoint</t>
+  </si>
+  <si>
+    <t>https://cosmos-policy-assistant-dev.documents.azure.com:443/</t>
+  </si>
+  <si>
+    <t>Cosmos database</t>
+  </si>
+  <si>
+    <t>policy-assistant</t>
+  </si>
+  <si>
+    <t>Cosmos conversations container</t>
+  </si>
+  <si>
+    <t>conversations</t>
+  </si>
+  <si>
+    <t>Cosmos messages container</t>
+  </si>
+  <si>
+    <t>messages</t>
+  </si>
+  <si>
+    <t>Cosmos memories container</t>
+  </si>
+  <si>
+    <t>memories</t>
+  </si>
+  <si>
+    <t>CORS — Local</t>
+  </si>
+  <si>
+    <t>http://localhost:5173</t>
+  </si>
+  <si>
+    <t>CORS — Hosted Dev</t>
+  </si>
+  <si>
+    <t>Development React Static Web App origin</t>
+  </si>
+  <si>
+    <t>⚠️ Exact URL should be recorded</t>
+  </si>
+  <si>
+    <t>Logging level</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Logging is implemented in the Function App; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>INFO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is the intended Development baseline, but we should verify the deployed Azure setting.</t>
+    </r>
+  </si>
+  <si>
+    <t>Feature flags</t>
+  </si>
+  <si>
+    <t>⚠️ Inventory current active flags</t>
+  </si>
+  <si>
+    <t>Redirect URI — LOCAL</t>
+  </si>
+  <si>
+    <t>API scope - dev</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>LOCAL</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Several test/development flags have existed, including </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FORCE_SUMMARY_FAILURE_TEST=false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MEMORY_DEV_VALIDATION_ENABLED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> during validation.</t>
+    </r>
+  </si>
+  <si>
+    <t>VITE_POLICY_API_URL_LOCAL_TEST</t>
+  </si>
+  <si>
+    <t>http://localhost:7071/api/policy-chat</t>
+  </si>
+  <si>
+    <t>VITE_ENTRA_CLIENT_ID</t>
+  </si>
+  <si>
+    <t>5bb05e71-63a7-47e9-838c-38f384c1474f</t>
+  </si>
+  <si>
+    <t>VITE_ENTRA_TENANT_ID</t>
+  </si>
+  <si>
+    <t>VITE_POLICY_API_SCOPE</t>
+  </si>
+  <si>
+    <t>api://cfc6f96e-9d3c-4b29-b09d-44bab3055d31/access_policy_assistant</t>
+  </si>
+  <si>
+    <t>VITE_POLICY_API_URL</t>
+  </si>
+  <si>
+    <t>React Development API URL</t>
+  </si>
+  <si>
+    <t>Local API URL</t>
+  </si>
+  <si>
+    <t>API Scope</t>
+  </si>
+  <si>
+    <t>rs-swa-policy-assistant-react-dev</t>
+  </si>
+  <si>
+    <t>Resource Group</t>
+  </si>
+  <si>
+    <t>rg-corp-policy-ai-rag-dev</t>
+  </si>
+  <si>
+    <t>West US 2</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Entra ID</t>
+  </si>
+  <si>
+    <t>React Client</t>
+  </si>
+  <si>
+    <t>Resource Name</t>
+  </si>
+  <si>
+    <t>Azure Static Web Apps</t>
+  </si>
+  <si>
+    <t>Cosmos Database</t>
+  </si>
+  <si>
+    <t>Entra ID - App Registration</t>
+  </si>
+  <si>
+    <t>Azure AI Search</t>
+  </si>
+  <si>
+    <t>Microsoft Foundry</t>
+  </si>
+  <si>
+    <t>polite-ground-0d2a97a1e.6.azurestaticapps.net</t>
+  </si>
+  <si>
+    <t>React Client - Hostname</t>
+  </si>
+  <si>
+    <t>VITE_ENTRA_REDIRECT_URI</t>
+  </si>
+  <si>
+    <t>Post-logout Redirect URI</t>
+  </si>
+  <si>
+    <t>policy-assist-orchestration-func-app-dev_group</t>
+  </si>
+  <si>
+    <t>Policy Orchestration - App Name</t>
+  </si>
+  <si>
+    <t>Policy Orchestration - Resource Group</t>
+  </si>
+  <si>
+    <t>policy-assist-orchestration-func-app-dev-cxarefhbeef6e6d7.westus3-01.azurewebsites.net</t>
+  </si>
+  <si>
+    <t>Policy Orchestration - Hostname</t>
+  </si>
+  <si>
+    <t>Policy Orchestration - App URL</t>
+  </si>
+  <si>
+    <t>Policy Orchestration - API endpoint</t>
+  </si>
+  <si>
+    <t>allowed origins</t>
+  </si>
+  <si>
+    <t>local development origin</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -37,7 +585,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,14 +593,102 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="5"/>
+      </top>
+      <bottom style="thick">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +966,1224 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:F24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9.06640625" style="8"/>
+    <col min="2" max="2" width="49.265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="107.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1">
+      <c r="A2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="39" customHeight="1">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="39" customHeight="1">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="39" customHeight="1">
+      <c r="A5" s="8">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="39" customHeight="1">
+      <c r="A6" s="8">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" ht="39" customHeight="1">
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="4" customFormat="1" ht="39" customHeight="1">
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="4" customFormat="1"/>
+    <row r="10" spans="1:6" s="4" customFormat="1"/>
+    <row r="11" spans="1:6" s="4" customFormat="1"/>
+    <row r="12" spans="1:6" s="4" customFormat="1"/>
+    <row r="13" spans="1:6" s="4" customFormat="1"/>
+    <row r="14" spans="1:6" s="9" customFormat="1">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" s="9" customFormat="1">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" s="9" customFormat="1">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17" spans="1:1" s="9" customFormat="1">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="18" spans="1:1" s="9" customFormat="1">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" s="9" customFormat="1">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:1" s="9" customFormat="1">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:1" s="9" customFormat="1">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1" s="9" customFormat="1">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:1" s="9" customFormat="1">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:1" s="9" customFormat="1">
+      <c r="A24" s="4"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{1AA44AB5-BA88-4087-8BD8-66809C4AD9A2}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{3261BD60-AECD-493A-8DA3-5F64CB9F27EF}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{0A6D074C-5198-41AA-A50F-A845996415C9}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{B9806E08-80F3-4891-B2F8-B381F7D9956D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B533998B-2713-4112-832E-F416EEB7DBB3}">
+  <dimension ref="A2:E134"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="37.06640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.46484375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="75.46484375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.1328125" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="18">
+      <c r="A2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickBot="1">
+      <c r="A3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" ht="52.15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="4" customFormat="1" ht="49.15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="4" customFormat="1" ht="61.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A13" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A17" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A18" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A19" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A21" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="4" customFormat="1" ht="37.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A22" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="49.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A23" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="4" customFormat="1" ht="47.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A25" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A26" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A27" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="16"/>
+    </row>
+    <row r="28" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A28" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A29" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="16"/>
+    </row>
+    <row r="30" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A30" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A31" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A32" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A33" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A34" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A35" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="36" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A36" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A37" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="16"/>
+    </row>
+    <row r="38" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A38" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" spans="1:5" s="4" customFormat="1" ht="38.35" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A39" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="4" customFormat="1" ht="31.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A40" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:5" s="4" customFormat="1" ht="31.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A41" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:5" s="4" customFormat="1" ht="31.9" customHeight="1" thickTop="1">
+      <c r="A42" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="4" customFormat="1" ht="37.25" customHeight="1">
+      <c r="A43" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="4" customFormat="1" ht="37.25" customHeight="1">
+      <c r="A44" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="4" customFormat="1" ht="37.25" customHeight="1">
+      <c r="A45" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="4" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A46" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="4" customFormat="1" ht="44.65" customHeight="1">
+      <c r="A47" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="4" customFormat="1" ht="36.75" customHeight="1">
+      <c r="A48" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" s="4" customFormat="1">
+      <c r="A49" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="4" customFormat="1">
+      <c r="A50" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="4" customFormat="1">
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:4" s="4" customFormat="1">
+      <c r="C52" s="8"/>
+    </row>
+    <row r="53" spans="1:4" s="4" customFormat="1">
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" s="4" customFormat="1">
+      <c r="C54" s="8"/>
+    </row>
+    <row r="55" spans="1:4" s="4" customFormat="1">
+      <c r="C55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" s="4" customFormat="1">
+      <c r="C56" s="8"/>
+    </row>
+    <row r="57" spans="1:4" s="4" customFormat="1">
+      <c r="C57" s="8"/>
+    </row>
+    <row r="58" spans="1:4" s="4" customFormat="1">
+      <c r="C58" s="8"/>
+    </row>
+    <row r="59" spans="1:4" s="4" customFormat="1">
+      <c r="C59" s="8"/>
+    </row>
+    <row r="60" spans="1:4" s="4" customFormat="1">
+      <c r="C60" s="8"/>
+    </row>
+    <row r="61" spans="1:4" s="4" customFormat="1">
+      <c r="C61" s="8"/>
+    </row>
+    <row r="62" spans="1:4" s="4" customFormat="1">
+      <c r="C62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" s="4" customFormat="1">
+      <c r="C63" s="8"/>
+    </row>
+    <row r="64" spans="1:4" s="4" customFormat="1">
+      <c r="C64" s="8"/>
+    </row>
+    <row r="65" spans="3:3" s="4" customFormat="1">
+      <c r="C65" s="8"/>
+    </row>
+    <row r="66" spans="3:3" s="4" customFormat="1">
+      <c r="C66" s="8"/>
+    </row>
+    <row r="67" spans="3:3" s="4" customFormat="1">
+      <c r="C67" s="8"/>
+    </row>
+    <row r="68" spans="3:3" s="4" customFormat="1">
+      <c r="C68" s="8"/>
+    </row>
+    <row r="69" spans="3:3" s="4" customFormat="1">
+      <c r="C69" s="8"/>
+    </row>
+    <row r="70" spans="3:3" s="4" customFormat="1">
+      <c r="C70" s="8"/>
+    </row>
+    <row r="71" spans="3:3" s="4" customFormat="1">
+      <c r="C71" s="8"/>
+    </row>
+    <row r="72" spans="3:3" s="4" customFormat="1">
+      <c r="C72" s="8"/>
+    </row>
+    <row r="73" spans="3:3" s="4" customFormat="1">
+      <c r="C73" s="8"/>
+    </row>
+    <row r="74" spans="3:3" s="4" customFormat="1">
+      <c r="C74" s="8"/>
+    </row>
+    <row r="75" spans="3:3" s="4" customFormat="1">
+      <c r="C75" s="8"/>
+    </row>
+    <row r="76" spans="3:3" s="4" customFormat="1">
+      <c r="C76" s="8"/>
+    </row>
+    <row r="77" spans="3:3" s="4" customFormat="1">
+      <c r="C77" s="8"/>
+    </row>
+    <row r="78" spans="3:3" s="4" customFormat="1">
+      <c r="C78" s="8"/>
+    </row>
+    <row r="79" spans="3:3" s="4" customFormat="1">
+      <c r="C79" s="8"/>
+    </row>
+    <row r="80" spans="3:3" s="4" customFormat="1">
+      <c r="C80" s="8"/>
+    </row>
+    <row r="81" spans="3:3" s="4" customFormat="1">
+      <c r="C81" s="8"/>
+    </row>
+    <row r="82" spans="3:3" s="4" customFormat="1">
+      <c r="C82" s="8"/>
+    </row>
+    <row r="83" spans="3:3" s="4" customFormat="1">
+      <c r="C83" s="8"/>
+    </row>
+    <row r="84" spans="3:3" s="4" customFormat="1">
+      <c r="C84" s="8"/>
+    </row>
+    <row r="85" spans="3:3" s="4" customFormat="1">
+      <c r="C85" s="8"/>
+    </row>
+    <row r="86" spans="3:3" s="4" customFormat="1">
+      <c r="C86" s="8"/>
+    </row>
+    <row r="87" spans="3:3" s="4" customFormat="1">
+      <c r="C87" s="8"/>
+    </row>
+    <row r="88" spans="3:3" s="4" customFormat="1">
+      <c r="C88" s="8"/>
+    </row>
+    <row r="89" spans="3:3" s="4" customFormat="1">
+      <c r="C89" s="8"/>
+    </row>
+    <row r="90" spans="3:3" s="4" customFormat="1">
+      <c r="C90" s="8"/>
+    </row>
+    <row r="91" spans="3:3" s="4" customFormat="1">
+      <c r="C91" s="8"/>
+    </row>
+    <row r="92" spans="3:3" s="4" customFormat="1">
+      <c r="C92" s="8"/>
+    </row>
+    <row r="93" spans="3:3" s="4" customFormat="1">
+      <c r="C93" s="8"/>
+    </row>
+    <row r="94" spans="3:3" s="4" customFormat="1">
+      <c r="C94" s="8"/>
+    </row>
+    <row r="95" spans="3:3" s="4" customFormat="1">
+      <c r="C95" s="8"/>
+    </row>
+    <row r="96" spans="3:3" s="4" customFormat="1">
+      <c r="C96" s="8"/>
+    </row>
+    <row r="97" spans="3:3" s="4" customFormat="1">
+      <c r="C97" s="8"/>
+    </row>
+    <row r="98" spans="3:3" s="4" customFormat="1">
+      <c r="C98" s="8"/>
+    </row>
+    <row r="99" spans="3:3" s="4" customFormat="1">
+      <c r="C99" s="8"/>
+    </row>
+    <row r="100" spans="3:3" s="4" customFormat="1">
+      <c r="C100" s="8"/>
+    </row>
+    <row r="101" spans="3:3" s="4" customFormat="1">
+      <c r="C101" s="8"/>
+    </row>
+    <row r="102" spans="3:3" s="4" customFormat="1">
+      <c r="C102" s="8"/>
+    </row>
+    <row r="103" spans="3:3" s="4" customFormat="1">
+      <c r="C103" s="8"/>
+    </row>
+    <row r="104" spans="3:3" s="4" customFormat="1">
+      <c r="C104" s="8"/>
+    </row>
+    <row r="105" spans="3:3" s="4" customFormat="1">
+      <c r="C105" s="8"/>
+    </row>
+    <row r="106" spans="3:3" s="4" customFormat="1">
+      <c r="C106" s="8"/>
+    </row>
+    <row r="107" spans="3:3" s="4" customFormat="1">
+      <c r="C107" s="8"/>
+    </row>
+    <row r="108" spans="3:3" s="4" customFormat="1">
+      <c r="C108" s="8"/>
+    </row>
+    <row r="109" spans="3:3" s="4" customFormat="1">
+      <c r="C109" s="8"/>
+    </row>
+    <row r="110" spans="3:3" s="4" customFormat="1">
+      <c r="C110" s="8"/>
+    </row>
+    <row r="111" spans="3:3" s="4" customFormat="1">
+      <c r="C111" s="8"/>
+    </row>
+    <row r="112" spans="3:3" s="4" customFormat="1">
+      <c r="C112" s="8"/>
+    </row>
+    <row r="113" spans="3:3" s="4" customFormat="1">
+      <c r="C113" s="8"/>
+    </row>
+    <row r="114" spans="3:3" s="4" customFormat="1">
+      <c r="C114" s="8"/>
+    </row>
+    <row r="115" spans="3:3" s="4" customFormat="1">
+      <c r="C115" s="8"/>
+    </row>
+    <row r="116" spans="3:3" s="4" customFormat="1">
+      <c r="C116" s="8"/>
+    </row>
+    <row r="117" spans="3:3" s="4" customFormat="1">
+      <c r="C117" s="8"/>
+    </row>
+    <row r="118" spans="3:3" s="4" customFormat="1">
+      <c r="C118" s="8"/>
+    </row>
+    <row r="119" spans="3:3" s="4" customFormat="1">
+      <c r="C119" s="8"/>
+    </row>
+    <row r="120" spans="3:3" s="4" customFormat="1">
+      <c r="C120" s="8"/>
+    </row>
+    <row r="121" spans="3:3" s="4" customFormat="1">
+      <c r="C121" s="8"/>
+    </row>
+    <row r="122" spans="3:3" s="4" customFormat="1">
+      <c r="C122" s="8"/>
+    </row>
+    <row r="123" spans="3:3" s="4" customFormat="1">
+      <c r="C123" s="8"/>
+    </row>
+    <row r="124" spans="3:3" s="4" customFormat="1">
+      <c r="C124" s="8"/>
+    </row>
+    <row r="125" spans="3:3" s="4" customFormat="1">
+      <c r="C125" s="8"/>
+    </row>
+    <row r="126" spans="3:3" s="4" customFormat="1">
+      <c r="C126" s="8"/>
+    </row>
+    <row r="127" spans="3:3" s="4" customFormat="1">
+      <c r="C127" s="8"/>
+    </row>
+    <row r="128" spans="3:3" s="4" customFormat="1">
+      <c r="C128" s="8"/>
+    </row>
+    <row r="129" spans="3:3" s="4" customFormat="1">
+      <c r="C129" s="8"/>
+    </row>
+    <row r="130" spans="3:3" s="4" customFormat="1">
+      <c r="C130" s="8"/>
+    </row>
+    <row r="131" spans="3:3" s="4" customFormat="1">
+      <c r="C131" s="8"/>
+    </row>
+    <row r="132" spans="3:3" s="4" customFormat="1">
+      <c r="C132" s="8"/>
+    </row>
+    <row r="133" spans="3:3" s="4" customFormat="1">
+      <c r="C133" s="8"/>
+    </row>
+    <row r="134" spans="3:3" s="4" customFormat="1">
+      <c r="C134" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E2" xr:uid="{B533998B-2713-4112-832E-F416EEB7DBB3}"/>
+  <hyperlinks>
+    <hyperlink ref="D25" r:id="rId1" xr:uid="{707B4AEA-84C0-45F0-83CF-B95D222CEF0C}"/>
+    <hyperlink ref="D29" r:id="rId2" xr:uid="{70A8D0C3-E0B2-4F2F-83AF-9747B6E83035}"/>
+    <hyperlink ref="D35" r:id="rId3" xr:uid="{536504B6-8F3C-4435-9041-0B02BF762068}"/>
+    <hyperlink ref="D36" r:id="rId4" xr:uid="{C05E4A5B-484B-4655-ABDB-E3459BFB3593}"/>
+    <hyperlink ref="D33" r:id="rId5" xr:uid="{2A1B9F95-857E-4E8B-A230-0387DE860A7C}"/>
+    <hyperlink ref="D34" r:id="rId6" xr:uid="{D78AE261-92E3-4559-8C1E-DDFDFBB9D509}"/>
+    <hyperlink ref="D47" r:id="rId7" xr:uid="{E4D6D68F-7FD7-442C-85C3-7FA1321A4E66}"/>
+    <hyperlink ref="D48" r:id="rId8" xr:uid="{0452FAAC-D4DC-4EAB-A918-5CEF2B0DF6DE}"/>
+    <hyperlink ref="D49" r:id="rId9" xr:uid="{78F6A8B5-8AB2-4DE7-A9D0-9784C3261C2E}"/>
+    <hyperlink ref="D50" r:id="rId10" xr:uid="{8256F156-C429-4736-BF47-AFED847DF6F4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>